--- a/artfynd/A 28766-2026 artfynd.xlsx
+++ b/artfynd/A 28766-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,49 +804,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135349715</v>
+        <v>135366835</v>
       </c>
       <c r="B3" t="n">
-        <v>107598</v>
+        <v>4782</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221849</v>
+        <v>102306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -855,13 +844,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590520</v>
+        <v>590546</v>
       </c>
       <c r="R3" t="n">
-        <v>6496223</v>
+        <v>6496299</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +898,24 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -925,6 +928,130 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135349715</v>
+      </c>
+      <c r="B4" t="n">
+        <v>107598</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Fridtuna hästhage, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>590520</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6496223</v>
+      </c>
+      <c r="S4" t="n">
+        <v>7</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Östra Husby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28766-2026 artfynd.xlsx
+++ b/artfynd/A 28766-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -801,6 +806,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349660</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -928,6 +938,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135366835</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1052,8 +1067,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349715</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28766-2026 artfynd.xlsx
+++ b/artfynd/A 28766-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135349660</v>
       </c>
       <c r="B2" t="n">
-        <v>106730</v>
+        <v>106785</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>135349715</v>
       </c>
       <c r="B4" t="n">
-        <v>107598</v>
+        <v>107653</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28766-2026 artfynd.xlsx
+++ b/artfynd/A 28766-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135349660</v>
       </c>
       <c r="B2" t="n">
-        <v>106785</v>
+        <v>106812</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>135349715</v>
       </c>
       <c r="B4" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28766-2026 artfynd.xlsx
+++ b/artfynd/A 28766-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135349660</v>
       </c>
       <c r="B2" t="n">
-        <v>106817</v>
+        <v>106819</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>135349715</v>
       </c>
       <c r="B4" t="n">
-        <v>107685</v>
+        <v>107687</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
